--- a/artfynd/A 46771-2024 artfynd.xlsx
+++ b/artfynd/A 46771-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290579</v>
+        <v>120290580</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566183</v>
+        <v>566060</v>
       </c>
       <c r="R2" t="n">
-        <v>7012124</v>
+        <v>7012074</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290580</v>
+        <v>120290579</v>
       </c>
       <c r="B3" t="n">
-        <v>86895</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566060</v>
+        <v>566183</v>
       </c>
       <c r="R3" t="n">
-        <v>7012074</v>
+        <v>7012124</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 46771-2024 artfynd.xlsx
+++ b/artfynd/A 46771-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290580</v>
+        <v>120290579</v>
       </c>
       <c r="B2" t="n">
-        <v>86895</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566060</v>
+        <v>566183</v>
       </c>
       <c r="R2" t="n">
-        <v>7012074</v>
+        <v>7012124</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290579</v>
+        <v>120290580</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566183</v>
+        <v>566060</v>
       </c>
       <c r="R3" t="n">
-        <v>7012124</v>
+        <v>7012074</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 46771-2024 artfynd.xlsx
+++ b/artfynd/A 46771-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>120290580</v>
       </c>
       <c r="B2" t="n">
-        <v>87973</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,12 +789,7 @@
         <v>120290579</v>
       </c>
       <c r="B3" t="n">
-        <v>82345</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46771-2024 artfynd.xlsx
+++ b/artfynd/A 46771-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120290580</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120290579</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>